--- a/Avance trabajo/outputs/tabla_descriptivos_apa.xlsx
+++ b/Avance trabajo/outputs/tabla_descriptivos_apa.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="38">
   <si>
     <t xml:space="preserve">Tabla 1</t>
   </si>
@@ -32,6 +32,12 @@
     <t xml:space="preserve">Desv. Est.</t>
   </si>
   <si>
+    <t xml:space="preserve">Mínimo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Máximo</t>
+  </si>
+  <si>
     <t xml:space="preserve">calculation</t>
   </si>
   <si>
@@ -41,13 +47,31 @@
     <t xml:space="preserve">1.00</t>
   </si>
   <si>
+    <t xml:space="preserve">-2.96</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.60</t>
+  </si>
+  <si>
     <t xml:space="preserve">fluency</t>
   </si>
   <si>
     <t xml:space="preserve">-0.00</t>
   </si>
   <si>
+    <t xml:space="preserve">-2.16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06</t>
+  </si>
+  <si>
     <t xml:space="preserve">problems</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-4.76</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.52</t>
   </si>
   <si>
     <t xml:space="preserve">educ2012_rec: Incomplete Secondary education</t>
@@ -469,6 +493,8 @@
     <col min="2" max="2" width="6.60375" hidden="0" customWidth="1"/>
     <col min="3" max="3" width="11.31875" hidden="0" customWidth="1"/>
     <col min="4" max="4" width="12.4975" hidden="0" customWidth="1"/>
+    <col min="5" max="5" width="8.96125" hidden="0" customWidth="1"/>
+    <col min="6" max="6" width="8.96125" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -494,164 +520,236 @@
       <c r="D3" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="E3" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B4" s="4" t="n">
         <v>10674</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>8</v>
+        <v>10</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="B5" s="4" t="n">
         <v>10681</v>
       </c>
       <c r="C5" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D5" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="D5" s="4" t="s">
-        <v>8</v>
+      <c r="E5" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="B6" s="4" t="n">
         <v>10677</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>8</v>
+        <v>10</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="B7" s="4" t="n">
         <v>1796</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>14</v>
+        <v>22</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="B8" s="4" t="n">
         <v>6247</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>14</v>
+        <v>22</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="B9" s="4" t="n">
         <v>1872</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>14</v>
+        <v>22</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="B10" s="4" t="n">
         <v>5525</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>14</v>
+        <v>22</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="B11" s="4" t="n">
         <v>5342</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>14</v>
+        <v>22</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F11" s="4" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="B12" s="4" t="n">
         <v>4144</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>14</v>
+        <v>22</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F12" s="4" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="B13" s="4" t="n">
         <v>5977</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>14</v>
+        <v>22</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F13" s="4" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="s">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="B14" s="5" t="n">
         <v>366</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>14</v>
+        <v>22</v>
+      </c>
+      <c r="E14" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="F14" s="5" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
     </row>
   </sheetData>
